--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260227_202059.xlsx
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
